--- a/Impact modelling/Correlations_food_municipalities_months.xlsx
+++ b/Impact modelling/Correlations_food_municipalities_months.xlsx
@@ -438,10 +438,10 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.5437661126299669</v>
+        <v>0.5550726476270136</v>
       </c>
       <c r="C2">
-        <v>11.26953789888355</v>
+        <v>10.05633519111345</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -453,10 +453,10 @@
         <v>11</v>
       </c>
       <c r="G2">
-        <v>0.7385484740664388</v>
+        <v>0.7461451630984408</v>
       </c>
       <c r="H2">
-        <v>4.127648582864645E-223</v>
+        <v>1.207317875555842E-160</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -464,10 +464,10 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0.6094225823212354</v>
+        <v>0.6319547980248663</v>
       </c>
       <c r="C3">
-        <v>10.68736103488649</v>
+        <v>10.1013415460497</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
@@ -479,7 +479,7 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>0.7809183499394521</v>
+        <v>0.7951522404748916</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -490,10 +490,10 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0.6983835877152569</v>
+        <v>0.6464579042047917</v>
       </c>
       <c r="C4">
-        <v>6.87125936575782</v>
+        <v>7.028586338309932</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -505,10 +505,10 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>0.8367723179795924</v>
+        <v>0.8050807140445378</v>
       </c>
       <c r="H4">
-        <v>7.207143488591346E-315</v>
+        <v>1.120432380878598E-242</v>
       </c>
     </row>
   </sheetData>

--- a/Impact modelling/Correlations_food_municipalities_months.xlsx
+++ b/Impact modelling/Correlations_food_municipalities_months.xlsx
@@ -438,10 +438,10 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.5550726476270136</v>
+        <v>0.4707613007797058</v>
       </c>
       <c r="C2">
-        <v>10.05633519111345</v>
+        <v>9.980430478623781</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -453,10 +453,10 @@
         <v>11</v>
       </c>
       <c r="G2">
-        <v>0.7461451630984408</v>
+        <v>0.6872803331049948</v>
       </c>
       <c r="H2">
-        <v>1.207317875555842E-160</v>
+        <v>8.141804490291411E-194</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -464,10 +464,10 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0.6319547980248663</v>
+        <v>0.5120873435274336</v>
       </c>
       <c r="C3">
-        <v>10.1013415460497</v>
+        <v>9.617794344970992</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
@@ -479,7 +479,7 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>0.7951522404748916</v>
+        <v>0.7156236162528946</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -490,10 +490,10 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0.6464579042047917</v>
+        <v>0.5738429824682878</v>
       </c>
       <c r="C4">
-        <v>7.028586338309932</v>
+        <v>8.276532900741687</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -505,10 +505,10 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>0.8050807140445378</v>
+        <v>0.7586434657754482</v>
       </c>
       <c r="H4">
-        <v>1.120432380878598E-242</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
